--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1320,6 +1325,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1468,6 +1478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1616,6 +1631,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2370,6 +2390,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2518,6 +2543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2666,6 +2696,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2962,6 +2997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3110,6 +3150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3406,6 +3451,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3554,6 +3604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3702,6 +3757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3850,6 +3910,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3998,6 +4063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4294,6 +4364,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4442,6 +4517,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5034,6 +5114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5182,6 +5267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5478,6 +5568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5626,6 +5721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5774,6 +5874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5922,6 +6027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6070,6 +6180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6218,6 +6333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6366,6 +6486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6910,6 +7035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7650,6 +7780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7798,6 +7933,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7946,6 +8086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8094,6 +8239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8242,6 +8392,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8390,6 +8545,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8538,6 +8698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8686,6 +8851,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8834,6 +9004,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8982,6 +9157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9130,6 +9310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9674,6 +9859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10414,6 +10604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10562,6 +10757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10710,6 +10910,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10858,6 +11063,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11006,6 +11216,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11154,6 +11369,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11302,6 +11522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11450,6 +11675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11598,6 +11828,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11746,6 +11981,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11894,6 +12134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12438,6 +12683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13178,6 +13428,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13326,6 +13581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13474,6 +13734,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13622,6 +13887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13918,6 +14188,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14066,6 +14341,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14214,6 +14494,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14362,6 +14647,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14510,6 +14800,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14658,6 +14953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14806,6 +15106,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15350,6 +15655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16090,6 +16400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16238,6 +16553,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16386,6 +16706,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16534,6 +16859,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16682,6 +17012,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16830,6 +17165,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16978,6 +17318,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17126,6 +17471,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17274,6 +17624,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17422,6 +17777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17570,6 +17930,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18114,6 +18479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18854,6 +19224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19002,6 +19377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19150,6 +19530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19298,6 +19683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19446,6 +19836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19594,6 +19989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19742,6 +20142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19890,6 +20295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20038,6 +20448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20186,6 +20601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20334,6 +20754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20878,6 +21303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21618,6 +22048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21766,6 +22201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21914,6 +22354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22062,6 +22507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22358,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22506,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22654,6 +23114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22802,6 +23267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22950,6 +23420,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23098,6 +23573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23246,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23790,6 +24275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24530,6 +25020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24678,6 +25173,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24826,6 +25326,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24974,6 +25479,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25122,6 +25632,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25270,6 +25785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25418,6 +25938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25566,6 +26091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25714,6 +26244,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25862,6 +26397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26010,6 +26550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26554,6 +27099,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27294,6 +27844,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27442,6 +27997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27590,6 +28150,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27738,6 +28303,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27886,6 +28456,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28034,6 +28609,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28182,6 +28762,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28330,6 +28915,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28478,6 +29068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28626,6 +29221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28774,6 +29374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29318,6 +29923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30206,6 +30816,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30354,6 +30969,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30502,6 +31122,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30650,6 +31275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30798,6 +31428,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30946,6 +31581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31094,6 +31734,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31242,6 +31887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31390,6 +32040,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31538,6 +32193,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31686,6 +32346,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32230,6 +32895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32970,6 +33640,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33118,6 +33793,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33266,6 +33946,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33414,6 +34099,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33562,6 +34252,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33710,6 +34405,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33858,6 +34558,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34006,6 +34711,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34154,6 +34864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34302,6 +35017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34450,6 +35170,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34994,6 +35719,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35734,6 +36464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35882,6 +36617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36030,6 +36770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36178,6 +36923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36326,6 +37076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36474,6 +37229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36622,6 +37382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36770,6 +37535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36918,6 +37688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37066,6 +37841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37214,6 +37994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37758,6 +38543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38646,6 +39436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39190,6 +39985,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39338,6 +40138,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39486,6 +40291,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40240,6 +41050,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40388,6 +41203,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40536,6 +41356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40832,6 +41657,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40980,6 +41810,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41276,6 +42111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41424,6 +42264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41572,6 +42417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41720,6 +42570,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41868,6 +42723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42164,6 +43024,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42312,6 +43177,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42904,6 +43774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43052,6 +43927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43348,6 +44228,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43496,6 +44381,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43644,6 +44534,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43792,6 +44687,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43940,6 +44840,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44088,6 +44993,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44236,6 +45146,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO286" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44780,6 +45695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO289" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45520,6 +46440,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45668,6 +46593,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45816,6 +46746,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO296" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45964,6 +46899,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46112,6 +47052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO298" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46260,6 +47205,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46408,6 +47358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46556,6 +47511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46704,6 +47664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46852,6 +47817,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47000,6 +47970,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47544,6 +48519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48284,6 +49264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO312" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48432,6 +49417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO313" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48580,6 +49570,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48728,6 +49723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO315" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48876,6 +49876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO316" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49024,6 +50029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO317" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49172,6 +50182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO318" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49320,6 +50335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49468,6 +50488,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO320" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49616,6 +50641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO321" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49764,6 +50794,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO322" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50308,6 +51343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO325" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51196,6 +52236,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO331" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51344,6 +52389,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO332" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51492,6 +52542,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO333" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51640,6 +52695,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO334" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51788,6 +52848,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51936,6 +53001,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO336" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52084,6 +53154,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA337" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO337" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52232,6 +53307,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52380,6 +53460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO339" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52528,6 +53613,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52676,6 +53766,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53220,6 +54315,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53960,6 +55060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO349" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54108,6 +55213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54256,6 +55366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54404,6 +55519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54552,6 +55672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO353" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54700,6 +55825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA354" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO354" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54848,6 +55978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO355" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54996,6 +56131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55144,6 +56284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO357" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55292,6 +56437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO358" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55440,6 +56590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO359" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55984,6 +57139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56724,6 +57884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56872,6 +58037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO368" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57020,6 +58190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO369" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57168,6 +58343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57316,6 +58496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57464,6 +58649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57612,6 +58802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57760,6 +58955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO374" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57908,6 +59108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58056,6 +59261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO376" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58204,6 +59414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO377" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -58748,6 +59963,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59636,6 +60856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO386" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59784,6 +61009,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59932,6 +61162,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60080,6 +61315,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO389" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60228,6 +61468,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60376,6 +61621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO391" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60524,6 +61774,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO392" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60672,6 +61927,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA393" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60820,6 +62080,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO394" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60968,6 +62233,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO395" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61116,6 +62386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO396" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61660,6 +62935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO399" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62400,6 +63680,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO404" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62548,6 +63833,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO405" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62696,6 +63986,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62844,6 +64139,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -62992,6 +64292,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO408" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63140,6 +64445,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA409" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO409" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63288,6 +64598,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA410" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO410" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63436,6 +64751,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63584,6 +64904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO412" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63732,6 +65057,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -63880,6 +65210,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -64424,6 +65759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO417" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65164,6 +66504,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO422" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65312,6 +66657,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65460,6 +66810,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65608,6 +66963,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -65904,6 +67264,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66052,6 +67417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66200,6 +67570,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66348,6 +67723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66496,6 +67876,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66644,6 +68029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -66792,6 +68182,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -67336,6 +68731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68076,6 +69476,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68224,6 +69629,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68372,6 +69782,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68520,6 +69935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO444" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68668,6 +70088,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68816,6 +70241,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -68964,6 +70394,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69112,6 +70547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO448" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69260,6 +70700,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO449" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69408,6 +70853,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -69556,6 +71006,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO451" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70100,6 +71555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO454" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70840,6 +72300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA459" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO459" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -70988,6 +72453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO460" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71136,6 +72606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO461" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71284,6 +72759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO462" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71432,6 +72912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO463" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71580,6 +73065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA464" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO464" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71728,6 +73218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA465" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO465" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -71876,6 +73371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA466" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO466" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72024,6 +73524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA467" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO467" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72172,6 +73677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA468" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO468" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72320,6 +73830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA469" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO469" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -72864,6 +74379,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO472" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73604,6 +75124,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA477" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO477" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73752,6 +75277,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA478" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO478" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -73900,6 +75430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA479" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO479" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74048,6 +75583,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA480" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO480" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74344,6 +75884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA482" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO482" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74492,6 +76037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA483" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO483" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74640,6 +76190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA484" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO484" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74788,6 +76343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA485" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO485" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -74936,6 +76496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA486" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO486" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75084,6 +76649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA487" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO487" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75232,6 +76802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA488" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO488" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -75774,6 +77349,11 @@
       <c r="S491" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA491" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO491" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_CH_f694197332056b74264617223b9b</t>
@@ -793,12 +788,7 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -808,11 +798,6 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -933,11 +918,6 @@
       <c r="R3" t="n">
         <v>2.162843048535928</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
@@ -950,22 +930,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1086,11 +1056,6 @@
       <c r="R4" t="n">
         <v>2.224638564208384</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>annual</t>
@@ -1103,22 +1068,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1239,11 +1194,6 @@
       <c r="R5" t="n">
         <v>6.500888248742276</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>annual</t>
@@ -1256,22 +1206,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1392,11 +1332,6 @@
       <c r="R6" t="n">
         <v>0.2719002689588024</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>SER_CH_TYPHOID_PARATYPHOID_COMBINED_ANNUAL</t>
@@ -1414,12 +1349,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1429,11 +1359,6 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1554,11 +1479,6 @@
       <c r="R7" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_CH_f9a83f885db35bef07faa5660c7d</t>
@@ -1576,12 +1496,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1591,11 +1506,6 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1716,11 +1626,6 @@
       <c r="R8" t="n">
         <v>0.04943641253796408</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_CH_469575ffcfe721f18095d3988572</t>
@@ -1738,12 +1643,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1753,11 +1653,6 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1878,11 +1773,6 @@
       <c r="R9" t="n">
         <v>1.977456501518563</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>annual</t>
@@ -1895,22 +1785,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2031,11 +1911,6 @@
       <c r="R10" t="n">
         <v>0.07415461880694611</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_CH_e028ac530b212500cdacefab82f4</t>
@@ -2053,12 +1928,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -2068,11 +1938,6 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2193,11 +2058,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -2215,12 +2075,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2230,11 +2085,6 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2355,11 +2205,6 @@
       <c r="R12" t="n">
         <v>0.04943641253796408</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>annual</t>
@@ -2372,22 +2217,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2508,11 +2343,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_CH_f886ae423245c4d4d945d22c04fa</t>
@@ -2530,12 +2360,7 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2545,11 +2370,6 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2670,11 +2490,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_CH_b72471754ba1860d0eddb1a769dc</t>
@@ -2692,12 +2507,7 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2707,11 +2517,6 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2832,11 +2637,6 @@
       <c r="R15" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_CH_a0517232b84d84ff4cd02f6351b8</t>
@@ -2854,12 +2654,7 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2869,11 +2664,6 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2994,11 +2784,6 @@
       <c r="R16" t="n">
         <v>1.050523766431737</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3011,22 +2796,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3147,11 +2922,6 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_CH_786c4b7daf62e750a64acefa1b6f</t>
@@ -3169,12 +2939,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -3184,11 +2949,6 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3309,11 +3069,6 @@
       <c r="R18" t="n">
         <v>11.22206564611784</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3326,22 +3081,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3462,11 +3207,6 @@
       <c r="R19" t="n">
         <v>3.485267083926467</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3479,22 +3219,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3615,11 +3345,6 @@
       <c r="R20" t="n">
         <v>0.8033417037419163</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3632,22 +3357,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3768,11 +3483,6 @@
       <c r="R21" t="n">
         <v>3.64593542467485</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3785,22 +3495,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3921,11 +3621,6 @@
       <c r="R22" t="n">
         <v>0.6179551567245509</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_CH_2ce78184086538bc0b855523c066</t>
@@ -3943,12 +3638,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -3958,11 +3648,6 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4083,11 +3768,6 @@
       <c r="R23" t="n">
         <v>0.3213366814967665</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>annual</t>
@@ -4100,22 +3780,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4236,11 +3906,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_CH_1e52604ac357d550ec3a557eaaa3</t>
@@ -4258,12 +3923,7 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -4273,11 +3933,6 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4398,11 +4053,6 @@
       <c r="R25" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_CH_d2c9bee662276d35e5e8c9d18cc3</t>
@@ -4420,12 +4070,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4435,11 +4080,6 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4560,11 +4200,6 @@
       <c r="R26" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_CH_7e04405263e8990535f6c1a7374d</t>
@@ -4582,12 +4217,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ26" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4597,11 +4227,6 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4722,11 +4347,6 @@
       <c r="R27" t="n">
         <v>0.2348229595553293</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_CH_d0b9b916925a9e694f207bd1375a</t>
@@ -4744,12 +4364,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ27" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4759,11 +4374,6 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4878,17 +4488,15 @@
       <c r="O28" t="n">
         <v>106</v>
       </c>
+      <c r="P28" t="n">
+        <v>106</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>1.310064932256048</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4901,22 +4509,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5031,17 +4629,15 @@
       <c r="O29" t="n">
         <v>167</v>
       </c>
+      <c r="P29" t="n">
+        <v>167</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>2.06397022346</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5054,22 +4650,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5184,17 +4770,15 @@
       <c r="O30" t="n">
         <v>253</v>
       </c>
+      <c r="P30" t="n">
+        <v>253</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>3.126853093026228</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5207,22 +4791,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5337,17 +4911,15 @@
       <c r="O31" t="n">
         <v>323</v>
       </c>
+      <c r="P31" t="n">
+        <v>323</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>3.991990312440599</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5360,22 +4932,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5496,11 +5058,6 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5513,22 +5070,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5643,17 +5190,15 @@
       <c r="O33" t="n">
         <v>392</v>
       </c>
+      <c r="P33" t="n">
+        <v>392</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>4.844768428720479</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5666,22 +5211,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5796,17 +5331,15 @@
       <c r="O34" t="n">
         <v>369</v>
       </c>
+      <c r="P34" t="n">
+        <v>369</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>4.560509056627185</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5819,22 +5352,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5949,17 +5472,15 @@
       <c r="O35" t="n">
         <v>295</v>
       </c>
+      <c r="P35" t="n">
+        <v>295</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>3.64593542467485</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5972,22 +5493,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6102,17 +5613,15 @@
       <c r="O36" t="n">
         <v>277</v>
       </c>
+      <c r="P36" t="n">
+        <v>277</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>3.423471568254012</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6125,22 +5634,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6261,11 +5760,6 @@
       <c r="R37" t="n">
         <v>1.21119210718012</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6278,22 +5772,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6408,17 +5892,15 @@
       <c r="O38" t="n">
         <v>235</v>
       </c>
+      <c r="P38" t="n">
+        <v>235</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>2.904389236605389</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6431,22 +5913,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6561,17 +6033,15 @@
       <c r="O39" t="n">
         <v>125</v>
       </c>
+      <c r="P39" t="n">
+        <v>125</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>1.544887891811377</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6584,22 +6054,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6714,17 +6174,15 @@
       <c r="O40" t="n">
         <v>99</v>
       </c>
+      <c r="P40" t="n">
+        <v>99</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>1.223551210314611</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6737,22 +6195,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6867,17 +6315,15 @@
       <c r="O41" t="n">
         <v>66</v>
       </c>
+      <c r="P41" t="n">
+        <v>66</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0.8157008068764073</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6890,22 +6336,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7020,17 +6456,15 @@
       <c r="O42" t="n">
         <v>45</v>
       </c>
+      <c r="P42" t="n">
+        <v>45</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0.5561596410520959</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7043,22 +6477,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7179,11 +6603,6 @@
       <c r="R43" t="n">
         <v>4.25153147826491</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7196,22 +6615,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7326,17 +6735,15 @@
       <c r="O44" t="n">
         <v>20</v>
       </c>
+      <c r="P44" t="n">
+        <v>20</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0.2471820626898204</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7349,22 +6756,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7479,17 +6876,15 @@
       <c r="O45" t="n">
         <v>11</v>
       </c>
+      <c r="P45" t="n">
+        <v>11</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0.1359501344794012</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7502,22 +6897,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7632,17 +7017,15 @@
       <c r="O46" t="n">
         <v>6</v>
       </c>
+      <c r="P46" t="n">
+        <v>6</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0.07415461880694611</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7655,22 +7038,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7785,17 +7158,15 @@
       <c r="O47" t="n">
         <v>6</v>
       </c>
+      <c r="P47" t="n">
+        <v>6</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0.07415461880694611</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7808,22 +7179,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7944,11 +7305,6 @@
       <c r="R48" t="n">
         <v>17.62408106978419</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7961,22 +7317,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -8091,17 +7437,15 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8114,22 +7458,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8244,17 +7578,15 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8267,22 +7599,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8397,17 +7719,15 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8420,22 +7740,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8550,17 +7860,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8573,22 +7881,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8709,11 +8007,6 @@
       <c r="R53" t="n">
         <v>30.39103460771342</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8726,22 +8019,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8856,17 +8139,15 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8879,22 +8160,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -9009,17 +8280,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9032,22 +8301,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9162,17 +8421,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9185,22 +8442,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9315,17 +8562,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9338,22 +8583,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9468,17 +8703,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9491,22 +8724,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9627,11 +8850,6 @@
       <c r="R59" t="n">
         <v>25.52154797272395</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9644,22 +8862,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9774,17 +8982,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9797,22 +9003,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9927,17 +9123,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9950,22 +9144,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -10080,17 +9264,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10103,22 +9285,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10233,17 +9405,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10256,22 +9426,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10392,11 +9552,6 @@
       <c r="R64" t="n">
         <v>30.39103460771342</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10409,22 +9564,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10539,17 +9684,15 @@
       <c r="O65" t="n">
         <v>2</v>
       </c>
+      <c r="P65" t="n">
+        <v>2</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0.02471820626898204</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10562,22 +9705,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10692,17 +9825,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10715,22 +9846,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10845,17 +9966,15 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10868,22 +9987,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10998,17 +10107,15 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11021,22 +10128,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11157,11 +10254,6 @@
       <c r="R69" t="n">
         <v>19.45322833368887</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11174,22 +10266,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11304,17 +10386,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11327,22 +10407,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11457,17 +10527,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11480,22 +10548,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11610,17 +10668,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11633,22 +10689,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11763,17 +10809,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11786,22 +10830,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11916,17 +10950,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11939,22 +10971,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -12075,11 +11097,6 @@
       <c r="R75" t="n">
         <v>12.75459443479473</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12092,22 +11109,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12222,17 +11229,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12245,22 +11250,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12375,17 +11370,15 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12398,22 +11391,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12528,17 +11511,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12551,22 +11532,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12681,17 +11652,15 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12704,22 +11673,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12840,11 +11799,6 @@
       <c r="R80" t="n">
         <v>12.75459443479473</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12857,22 +11811,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12987,17 +11931,15 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13010,22 +11952,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13140,17 +12072,15 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13163,22 +12093,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13293,17 +12213,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13316,22 +12234,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13446,17 +12354,15 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
+      <c r="P84" t="n">
+        <v>2</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0.02471820626898204</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13469,22 +12375,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13605,11 +12501,6 @@
       <c r="R85" t="n">
         <v>7.2918708493497</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13622,22 +12513,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13752,17 +12633,15 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
+      <c r="P86" t="n">
+        <v>1</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0.01235910313449102</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13775,22 +12654,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13905,17 +12774,15 @@
       <c r="O87" t="n">
         <v>3</v>
       </c>
+      <c r="P87" t="n">
+        <v>3</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0.03707730940347306</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13928,22 +12795,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -14058,17 +12915,15 @@
       <c r="O88" t="n">
         <v>5</v>
       </c>
+      <c r="P88" t="n">
+        <v>5</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0.06179551567245509</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14081,22 +12936,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14211,17 +13056,15 @@
       <c r="O89" t="n">
         <v>11</v>
       </c>
+      <c r="P89" t="n">
+        <v>11</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0.1359501344794012</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14234,22 +13077,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14364,17 +13197,15 @@
       <c r="O90" t="n">
         <v>33</v>
       </c>
+      <c r="P90" t="n">
+        <v>33</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0.4078504034382037</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14387,22 +13218,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14523,11 +13344,6 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_CH_f694197332056b74264617223b9b</t>
@@ -14545,12 +13361,7 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ91" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -14560,11 +13371,6 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14685,11 +13491,6 @@
       <c r="R92" t="n">
         <v>0.2808222059060451</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>annual</t>
@@ -14702,22 +13503,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14838,11 +13629,6 @@
       <c r="R93" t="n">
         <v>1.550626963046423</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>annual</t>
@@ -14855,22 +13641,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14991,11 +13767,6 @@
       <c r="R94" t="n">
         <v>5.799589035016148</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>annual</t>
@@ -15008,22 +13779,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -15144,11 +13905,6 @@
       <c r="R95" t="n">
         <v>0.2930318670323949</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>SER_CH_TYPHOID_PARATYPHOID_COMBINED_ANNUAL</t>
@@ -15166,12 +13922,7 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -15181,11 +13932,6 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15306,11 +14052,6 @@
       <c r="R96" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_CH_f9a83f885db35bef07faa5660c7d</t>
@@ -15328,12 +14069,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -15343,11 +14079,6 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15468,11 +14199,6 @@
       <c r="R97" t="n">
         <v>0.03662898337904936</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_CH_469575ffcfe721f18095d3988572</t>
@@ -15490,12 +14216,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -15505,11 +14226,6 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15630,11 +14346,6 @@
       <c r="R98" t="n">
         <v>3.687317660157635</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>annual</t>
@@ -15647,22 +14358,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15783,11 +14484,6 @@
       <c r="R99" t="n">
         <v>0.04883864450539914</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_CH_e028ac530b212500cdacefab82f4</t>
@@ -15805,12 +14501,7 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -15820,11 +14511,6 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15945,11 +14631,6 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -15967,12 +14648,7 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -15982,11 +14658,6 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -16107,11 +14778,6 @@
       <c r="R101" t="n">
         <v>1.001192212360682</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>annual</t>
@@ -16124,22 +14790,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -16260,11 +14916,6 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_CH_f886ae423245c4d4d945d22c04fa</t>
@@ -16282,12 +14933,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -16297,11 +14943,6 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16422,11 +15063,6 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_CH_b72471754ba1860d0eddb1a769dc</t>
@@ -16444,12 +15080,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -16459,11 +15090,6 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16584,11 +15210,6 @@
       <c r="R104" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_CH_a0517232b84d84ff4cd02f6351b8</t>
@@ -16606,12 +15227,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -16621,11 +15237,6 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16746,11 +15357,6 @@
       <c r="R105" t="n">
         <v>1.208756451508629</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>annual</t>
@@ -16763,22 +15369,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -16899,11 +15495,6 @@
       <c r="R106" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_CH_786c4b7daf62e750a64acefa1b6f</t>
@@ -16921,12 +15512,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -16936,11 +15522,6 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
-      </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -17061,11 +15642,6 @@
       <c r="R107" t="n">
         <v>9.60900330643728</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>annual</t>
@@ -17078,22 +15654,12 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
-      </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -17214,11 +15780,6 @@
       <c r="R108" t="n">
         <v>3.601850032273187</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>annual</t>
@@ -17231,22 +15792,12 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
-      </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -17367,11 +15918,6 @@
       <c r="R109" t="n">
         <v>1.220966112634979</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>annual</t>
@@ -17384,22 +15930,12 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
-      </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -17520,11 +16056,6 @@
       <c r="R110" t="n">
         <v>3.504172743262389</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17537,22 +16068,12 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -17673,11 +16194,6 @@
       <c r="R111" t="n">
         <v>0.4639671228012918</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_CH_2ce78184086538bc0b855523c066</t>
@@ -17695,12 +16211,7 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -17710,11 +16221,6 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
-      </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -17835,11 +16341,6 @@
       <c r="R112" t="n">
         <v>0.4883864450539914</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>annual</t>
@@ -17852,22 +16353,12 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
-      </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -17988,11 +16479,6 @@
       <c r="R113" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_CH_1e52604ac357d550ec3a557eaaa3</t>
@@ -18010,12 +16496,7 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ113" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -18025,11 +16506,6 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
-      </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -18150,11 +16626,6 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_CH_d2c9bee662276d35e5e8c9d18cc3</t>
@@ -18172,12 +16643,7 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ114" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -18187,11 +16653,6 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
-      </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -18312,11 +16773,6 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_CH_7e04405263e8990535f6c1a7374d</t>
@@ -18334,12 +16790,7 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ115" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -18349,11 +16800,6 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -18474,11 +16920,6 @@
       <c r="R116" t="n">
         <v>0.2319835614006459</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_CH_d0b9b916925a9e694f207bd1375a</t>
@@ -18496,12 +16937,7 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ116" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -18511,11 +16947,6 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
-        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -18630,17 +17061,15 @@
       <c r="O117" t="n">
         <v>68</v>
       </c>
+      <c r="P117" t="n">
+        <v>68</v>
+      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0.8302569565917854</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18653,22 +17082,12 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -18783,17 +17202,15 @@
       <c r="O118" t="n">
         <v>69</v>
       </c>
+      <c r="P118" t="n">
+        <v>69</v>
+      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0.8424666177181351</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18806,22 +17223,12 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -18936,17 +17343,15 @@
       <c r="O119" t="n">
         <v>56</v>
       </c>
+      <c r="P119" t="n">
+        <v>56</v>
+      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0.683741023075588</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18959,22 +17364,12 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -19089,17 +17484,15 @@
       <c r="O120" t="n">
         <v>74</v>
       </c>
+      <c r="P120" t="n">
+        <v>74</v>
+      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.9035149233498841</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19112,22 +17505,12 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -19248,11 +17631,6 @@
       <c r="R121" t="n">
         <v>1.758191202194369</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19265,22 +17643,12 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -19395,17 +17763,15 @@
       <c r="O122" t="n">
         <v>148</v>
       </c>
+      <c r="P122" t="n">
+        <v>148</v>
+      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>1.807029846699768</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19418,22 +17784,12 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -19548,17 +17904,15 @@
       <c r="O123" t="n">
         <v>159</v>
       </c>
+      <c r="P123" t="n">
+        <v>159</v>
+      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>1.941336119089616</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19571,22 +17925,12 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -19701,17 +18045,15 @@
       <c r="O124" t="n">
         <v>164</v>
       </c>
+      <c r="P124" t="n">
+        <v>164</v>
+      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>2.002384424721364</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19724,22 +18066,12 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -19854,17 +18186,15 @@
       <c r="O125" t="n">
         <v>146</v>
       </c>
+      <c r="P125" t="n">
+        <v>146</v>
+      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>1.782610524447068</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19877,22 +18207,12 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -20013,11 +18333,6 @@
       <c r="R126" t="n">
         <v>0.5738540729384399</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20030,22 +18345,12 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -20160,17 +18465,15 @@
       <c r="O127" t="n">
         <v>131</v>
       </c>
+      <c r="P127" t="n">
+        <v>131</v>
+      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>1.599465607551822</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20183,22 +18486,12 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -20313,17 +18606,15 @@
       <c r="O128" t="n">
         <v>157</v>
       </c>
+      <c r="P128" t="n">
+        <v>157</v>
+      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>1.916916796836916</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20336,22 +18627,12 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -20466,17 +18747,15 @@
       <c r="O129" t="n">
         <v>109</v>
       </c>
+      <c r="P129" t="n">
+        <v>109</v>
+      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>1.330853062772127</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20489,22 +18768,12 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -20619,17 +18888,15 @@
       <c r="O130" t="n">
         <v>89</v>
       </c>
+      <c r="P130" t="n">
+        <v>89</v>
+      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>1.086659840245131</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20642,22 +18909,12 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -20772,17 +19029,15 @@
       <c r="O131" t="n">
         <v>38</v>
       </c>
+      <c r="P131" t="n">
+        <v>38</v>
+      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0.4639671228012918</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20795,22 +19050,12 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -20931,11 +19176,6 @@
       <c r="R132" t="n">
         <v>4.090236477327179</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20948,22 +19188,12 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -21078,17 +19308,15 @@
       <c r="O133" t="n">
         <v>33</v>
       </c>
+      <c r="P133" t="n">
+        <v>33</v>
+      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0.4029188171695429</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21101,22 +19329,12 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -21231,17 +19449,15 @@
       <c r="O134" t="n">
         <v>24</v>
       </c>
+      <c r="P134" t="n">
+        <v>24</v>
+      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0.2930318670323949</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21254,22 +19470,12 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -21384,17 +19590,15 @@
       <c r="O135" t="n">
         <v>15</v>
       </c>
+      <c r="P135" t="n">
+        <v>15</v>
+      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0.1831449168952468</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21407,22 +19611,12 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -21537,17 +19731,15 @@
       <c r="O136" t="n">
         <v>11</v>
       </c>
+      <c r="P136" t="n">
+        <v>11</v>
+      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0.1343062723898477</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21560,22 +19752,12 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -21696,11 +19878,6 @@
       <c r="R137" t="n">
         <v>9.938664156848725</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21713,22 +19890,12 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -21843,17 +20010,15 @@
       <c r="O138" t="n">
         <v>7</v>
       </c>
+      <c r="P138" t="n">
+        <v>7</v>
+      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0.0854676278844485</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21866,22 +20031,12 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -21996,17 +20151,15 @@
       <c r="O139" t="n">
         <v>5</v>
       </c>
+      <c r="P139" t="n">
+        <v>5</v>
+      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0.06104830563174893</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22019,22 +20172,12 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -22149,17 +20292,15 @@
       <c r="O140" t="n">
         <v>2</v>
       </c>
+      <c r="P140" t="n">
+        <v>2</v>
+      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22172,22 +20313,12 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -22302,17 +20433,15 @@
       <c r="O141" t="n">
         <v>2</v>
       </c>
+      <c r="P141" t="n">
+        <v>2</v>
+      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22325,22 +20454,12 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -22461,11 +20580,6 @@
       <c r="R142" t="n">
         <v>13.45504656123746</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22478,22 +20592,12 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -22608,17 +20712,15 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
+      <c r="P143" t="n">
+        <v>0</v>
+      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22631,22 +20733,12 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -22761,17 +20853,15 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
+      <c r="P144" t="n">
+        <v>0</v>
+      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22784,22 +20874,12 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -22914,17 +20994,15 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
+      <c r="P145" t="n">
+        <v>1</v>
+      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22937,22 +21015,12 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -23067,17 +21135,15 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
+      <c r="P146" t="n">
+        <v>2</v>
+      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23090,22 +21156,12 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -23220,17 +21276,15 @@
       <c r="O147" t="n">
         <v>3</v>
       </c>
+      <c r="P147" t="n">
+        <v>3</v>
+      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0.03662898337904936</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23243,22 +21297,12 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -23379,11 +21423,6 @@
       <c r="R148" t="n">
         <v>21.64772917701817</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23396,22 +21435,12 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -23526,17 +21555,15 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
+      <c r="P149" t="n">
+        <v>2</v>
+      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23549,22 +21576,12 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -23679,17 +21696,15 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
+      <c r="P150" t="n">
+        <v>1</v>
+      </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23702,22 +21717,12 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -23832,17 +21837,15 @@
       <c r="O151" t="n">
         <v>5</v>
       </c>
+      <c r="P151" t="n">
+        <v>5</v>
+      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0.06104830563174893</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23855,22 +21858,12 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -23985,17 +21978,15 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
+      <c r="P152" t="n">
+        <v>2</v>
+      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24008,22 +21999,12 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -24144,11 +22125,6 @@
       <c r="R153" t="n">
         <v>8.778746349845495</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24161,22 +22137,12 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -24291,17 +22257,15 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24314,22 +22278,12 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
-      </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -24444,17 +22398,15 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24467,22 +22419,12 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -24597,17 +22539,15 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24620,22 +22560,12 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
-      </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -24750,17 +22680,15 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24773,22 +22701,12 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
-      </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -24903,17 +22821,15 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
+      <c r="P158" t="n">
+        <v>1</v>
+      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24926,22 +22842,12 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -25062,11 +22968,6 @@
       <c r="R159" t="n">
         <v>11.6968553590431</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25079,22 +22980,12 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
-      </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -25209,17 +23100,15 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
+      <c r="P160" t="n">
+        <v>1</v>
+      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25232,22 +23121,12 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -25362,17 +23241,15 @@
       <c r="O161" t="n">
         <v>2</v>
       </c>
+      <c r="P161" t="n">
+        <v>2</v>
+      </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25385,22 +23262,12 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
-      </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -25515,17 +23382,15 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
+      <c r="P162" t="n">
+        <v>1</v>
+      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25538,22 +23403,12 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -25668,17 +23523,15 @@
       <c r="O163" t="n">
         <v>2</v>
       </c>
+      <c r="P163" t="n">
+        <v>2</v>
+      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25691,22 +23544,12 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
-      </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -25827,11 +23670,6 @@
       <c r="R164" t="n">
         <v>8.192682615780706</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25844,22 +23682,12 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -25974,17 +23802,15 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25997,22 +23823,12 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
-      </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -26127,17 +23943,15 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26150,22 +23964,12 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
-      </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -26280,17 +24084,15 @@
       <c r="O167" t="n">
         <v>4</v>
       </c>
+      <c r="P167" t="n">
+        <v>4</v>
+      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0.04883864450539914</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26303,22 +24105,12 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
-      </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -26433,17 +24225,15 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26456,22 +24246,12 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
-      </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -26592,11 +24372,6 @@
       <c r="R169" t="n">
         <v>2.918109009197599</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26609,22 +24384,12 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
-      </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -26739,17 +24504,15 @@
       <c r="O170" t="n">
         <v>2</v>
       </c>
+      <c r="P170" t="n">
+        <v>2</v>
+      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0.02441932225269957</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26762,22 +24525,12 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
-      </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -26892,17 +24645,15 @@
       <c r="O171" t="n">
         <v>4</v>
       </c>
+      <c r="P171" t="n">
+        <v>4</v>
+      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0.04883864450539914</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -26915,22 +24666,12 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
-      </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -27045,17 +24786,15 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
+      <c r="P172" t="n">
+        <v>1</v>
+      </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>0.01220966112634978</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27068,22 +24807,12 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
-      </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -27198,17 +24927,15 @@
       <c r="O173" t="n">
         <v>4</v>
       </c>
+      <c r="P173" t="n">
+        <v>4</v>
+      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0.04883864450539914</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27221,22 +24948,12 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
-      </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -27351,17 +25068,15 @@
       <c r="O174" t="n">
         <v>6</v>
       </c>
+      <c r="P174" t="n">
+        <v>6</v>
+      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0.07325796675809872</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27374,22 +25089,12 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
-      </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -27510,11 +25215,6 @@
       <c r="R175" t="n">
         <v>1.15991780700323</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27527,22 +25227,12 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
-      </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -27657,17 +25347,15 @@
       <c r="O176" t="n">
         <v>12</v>
       </c>
+      <c r="P176" t="n">
+        <v>12</v>
+      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0.1465159335161974</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27680,22 +25368,12 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
-      </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -27810,17 +25488,15 @@
       <c r="O177" t="n">
         <v>24</v>
       </c>
+      <c r="P177" t="n">
+        <v>24</v>
+      </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>0.2930318670323949</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27833,22 +25509,12 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -27963,17 +25629,15 @@
       <c r="O178" t="n">
         <v>26</v>
       </c>
+      <c r="P178" t="n">
+        <v>26</v>
+      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0.3174511892850944</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -27986,22 +25650,12 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
-      </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -28116,17 +25770,15 @@
       <c r="O179" t="n">
         <v>75</v>
       </c>
+      <c r="P179" t="n">
+        <v>75</v>
+      </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0.9157245844762339</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -28139,22 +25791,12 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
-      </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -771,6 +771,11 @@
       <c r="R2" t="n">
         <v>0</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>HOLD_CH_f694197332056b74264617223b9b</t>
@@ -788,7 +793,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -798,6 +808,11 @@
       </c>
       <c r="AT2" t="n">
         <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,6 +933,11 @@
       <c r="R3" t="n">
         <v>2.162843048535928</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>annual</t>
@@ -930,12 +950,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1056,6 +1086,11 @@
       <c r="R4" t="n">
         <v>2.224638564208384</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>annual</t>
@@ -1068,12 +1103,22 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1194,6 +1239,11 @@
       <c r="R5" t="n">
         <v>6.500888248742276</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>annual</t>
@@ -1206,12 +1256,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1332,6 +1392,11 @@
       <c r="R6" t="n">
         <v>0.2719002689588024</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>SER_CH_TYPHOID_PARATYPHOID_COMBINED_ANNUAL</t>
@@ -1349,7 +1414,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1359,6 +1429,11 @@
       </c>
       <c r="AT6" t="n">
         <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1479,6 +1554,11 @@
       <c r="R7" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>HOLD_CH_f9a83f885db35bef07faa5660c7d</t>
@@ -1496,7 +1576,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -1506,6 +1591,11 @@
       </c>
       <c r="AT7" t="n">
         <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1626,6 +1716,11 @@
       <c r="R8" t="n">
         <v>0.04943641253796408</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>HOLD_CH_469575ffcfe721f18095d3988572</t>
@@ -1643,7 +1738,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -1653,6 +1753,11 @@
       </c>
       <c r="AT8" t="n">
         <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1773,6 +1878,11 @@
       <c r="R9" t="n">
         <v>1.977456501518563</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>annual</t>
@@ -1785,12 +1895,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1911,6 +2031,11 @@
       <c r="R10" t="n">
         <v>0.07415461880694611</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>HOLD_CH_e028ac530b212500cdacefab82f4</t>
@@ -1928,7 +2053,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -1938,6 +2068,11 @@
       </c>
       <c r="AT10" t="n">
         <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2058,6 +2193,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -2075,7 +2215,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -2085,6 +2230,11 @@
       </c>
       <c r="AT11" t="n">
         <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2205,6 +2355,11 @@
       <c r="R12" t="n">
         <v>0.04943641253796408</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>annual</t>
@@ -2217,12 +2372,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2343,6 +2508,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>HOLD_CH_f886ae423245c4d4d945d22c04fa</t>
@@ -2360,7 +2530,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -2370,6 +2545,11 @@
       </c>
       <c r="AT13" t="n">
         <v>1</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2490,6 +2670,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>HOLD_CH_b72471754ba1860d0eddb1a769dc</t>
@@ -2507,7 +2692,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -2517,6 +2707,11 @@
       </c>
       <c r="AT14" t="n">
         <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2637,6 +2832,11 @@
       <c r="R15" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>HOLD_CH_a0517232b84d84ff4cd02f6351b8</t>
@@ -2654,7 +2854,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -2664,6 +2869,11 @@
       </c>
       <c r="AT15" t="n">
         <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2784,6 +2994,11 @@
       <c r="R16" t="n">
         <v>1.050523766431737</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>annual</t>
@@ -2796,12 +3011,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -2922,6 +3147,11 @@
       <c r="R17" t="n">
         <v>0</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>HOLD_CH_786c4b7daf62e750a64acefa1b6f</t>
@@ -2939,7 +3169,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -2949,6 +3184,11 @@
       </c>
       <c r="AT17" t="n">
         <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3069,6 +3309,11 @@
       <c r="R18" t="n">
         <v>11.22206564611784</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3081,12 +3326,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3207,6 +3462,11 @@
       <c r="R19" t="n">
         <v>3.485267083926467</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3219,12 +3479,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3345,6 +3615,11 @@
       <c r="R20" t="n">
         <v>0.8033417037419163</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3357,12 +3632,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3483,6 +3768,11 @@
       <c r="R21" t="n">
         <v>3.64593542467485</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3495,12 +3785,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3621,6 +3921,11 @@
       <c r="R22" t="n">
         <v>0.6179551567245509</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>HOLD_CH_2ce78184086538bc0b855523c066</t>
@@ -3638,7 +3943,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -3648,6 +3958,11 @@
       </c>
       <c r="AT22" t="n">
         <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3768,6 +4083,11 @@
       <c r="R23" t="n">
         <v>0.3213366814967665</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>annual</t>
@@ -3780,12 +4100,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3906,6 +4236,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>HOLD_CH_1e52604ac357d550ec3a557eaaa3</t>
@@ -3923,7 +4258,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -3933,6 +4273,11 @@
       </c>
       <c r="AT24" t="n">
         <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4053,6 +4398,11 @@
       <c r="R25" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>HOLD_CH_d2c9bee662276d35e5e8c9d18cc3</t>
@@ -4070,7 +4420,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -4080,6 +4435,11 @@
       </c>
       <c r="AT25" t="n">
         <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4200,6 +4560,11 @@
       <c r="R26" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>HOLD_CH_7e04405263e8990535f6c1a7374d</t>
@@ -4217,7 +4582,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -4227,6 +4597,11 @@
       </c>
       <c r="AT26" t="n">
         <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4347,6 +4722,11 @@
       <c r="R27" t="n">
         <v>0.2348229595553293</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>HOLD_CH_d0b9b916925a9e694f207bd1375a</t>
@@ -4364,7 +4744,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -4374,6 +4759,11 @@
       </c>
       <c r="AT27" t="n">
         <v>1</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4488,15 +4878,17 @@
       <c r="O28" t="n">
         <v>106</v>
       </c>
-      <c r="P28" t="n">
-        <v>106</v>
-      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>1.310064932256048</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4509,12 +4901,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4629,15 +5031,17 @@
       <c r="O29" t="n">
         <v>167</v>
       </c>
-      <c r="P29" t="n">
-        <v>167</v>
-      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>2.06397022346</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4650,12 +5054,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4770,15 +5184,17 @@
       <c r="O30" t="n">
         <v>253</v>
       </c>
-      <c r="P30" t="n">
-        <v>253</v>
-      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>3.126853093026228</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4791,12 +5207,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4911,15 +5337,17 @@
       <c r="O31" t="n">
         <v>323</v>
       </c>
-      <c r="P31" t="n">
-        <v>323</v>
-      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>3.991990312440599</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4932,12 +5360,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5058,6 +5496,11 @@
       <c r="R32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5070,12 +5513,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5190,15 +5643,17 @@
       <c r="O33" t="n">
         <v>392</v>
       </c>
-      <c r="P33" t="n">
-        <v>392</v>
-      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>4.844768428720479</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5211,12 +5666,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5331,15 +5796,17 @@
       <c r="O34" t="n">
         <v>369</v>
       </c>
-      <c r="P34" t="n">
-        <v>369</v>
-      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>4.560509056627185</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5352,12 +5819,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5472,15 +5949,17 @@
       <c r="O35" t="n">
         <v>295</v>
       </c>
-      <c r="P35" t="n">
-        <v>295</v>
-      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>3.64593542467485</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5493,12 +5972,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5613,15 +6102,17 @@
       <c r="O36" t="n">
         <v>277</v>
       </c>
-      <c r="P36" t="n">
-        <v>277</v>
-      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>3.423471568254012</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5634,12 +6125,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5760,6 +6261,11 @@
       <c r="R37" t="n">
         <v>1.21119210718012</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5772,12 +6278,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -5892,15 +6408,17 @@
       <c r="O38" t="n">
         <v>235</v>
       </c>
-      <c r="P38" t="n">
-        <v>235</v>
-      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>2.904389236605389</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5913,12 +6431,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6033,15 +6561,17 @@
       <c r="O39" t="n">
         <v>125</v>
       </c>
-      <c r="P39" t="n">
-        <v>125</v>
-      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>1.544887891811377</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6054,12 +6584,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6174,15 +6714,17 @@
       <c r="O40" t="n">
         <v>99</v>
       </c>
-      <c r="P40" t="n">
-        <v>99</v>
-      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>1.223551210314611</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6195,12 +6737,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6315,15 +6867,17 @@
       <c r="O41" t="n">
         <v>66</v>
       </c>
-      <c r="P41" t="n">
-        <v>66</v>
-      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0.8157008068764073</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6336,12 +6890,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6456,15 +7020,17 @@
       <c r="O42" t="n">
         <v>45</v>
       </c>
-      <c r="P42" t="n">
-        <v>45</v>
-      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0.5561596410520959</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6477,12 +7043,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -6603,6 +7179,11 @@
       <c r="R43" t="n">
         <v>4.25153147826491</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6615,12 +7196,22 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -6735,15 +7326,17 @@
       <c r="O44" t="n">
         <v>20</v>
       </c>
-      <c r="P44" t="n">
-        <v>20</v>
-      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0.2471820626898204</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6756,12 +7349,22 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -6876,15 +7479,17 @@
       <c r="O45" t="n">
         <v>11</v>
       </c>
-      <c r="P45" t="n">
-        <v>11</v>
-      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0.1359501344794012</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6897,12 +7502,22 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7017,15 +7632,17 @@
       <c r="O46" t="n">
         <v>6</v>
       </c>
-      <c r="P46" t="n">
-        <v>6</v>
-      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0.07415461880694611</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7038,12 +7655,22 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7158,15 +7785,17 @@
       <c r="O47" t="n">
         <v>6</v>
       </c>
-      <c r="P47" t="n">
-        <v>6</v>
-      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0.07415461880694611</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7179,12 +7808,22 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7305,6 +7944,11 @@
       <c r="R48" t="n">
         <v>17.62408106978419</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7317,12 +7961,22 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7437,15 +8091,17 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7458,12 +8114,22 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -7578,15 +8244,17 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7599,12 +8267,22 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -7719,15 +8397,17 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7740,12 +8420,22 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -7860,15 +8550,17 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7881,12 +8573,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8007,6 +8709,11 @@
       <c r="R53" t="n">
         <v>30.39103460771342</v>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8019,12 +8726,22 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8139,15 +8856,17 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8160,12 +8879,22 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8280,15 +9009,17 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8301,12 +9032,22 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -8421,15 +9162,17 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8442,12 +9185,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -8562,15 +9315,17 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8583,12 +9338,22 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -8703,15 +9468,17 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8724,12 +9491,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -8850,6 +9627,11 @@
       <c r="R59" t="n">
         <v>25.52154797272395</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8862,12 +9644,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -8982,15 +9774,17 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9003,12 +9797,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9123,15 +9927,17 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9144,12 +9950,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9264,15 +10080,17 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9285,12 +10103,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -9405,15 +10233,17 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9426,12 +10256,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -9552,6 +10392,11 @@
       <c r="R64" t="n">
         <v>30.39103460771342</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9564,12 +10409,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -9684,15 +10539,17 @@
       <c r="O65" t="n">
         <v>2</v>
       </c>
-      <c r="P65" t="n">
-        <v>2</v>
-      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0.02471820626898204</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9705,12 +10562,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -9825,15 +10692,17 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="P66" t="n">
-        <v>0</v>
-      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9846,12 +10715,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -9966,15 +10845,17 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="P67" t="n">
-        <v>1</v>
-      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9987,12 +10868,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10107,15 +10998,17 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
-      <c r="P68" t="n">
-        <v>1</v>
-      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10128,12 +11021,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -10254,6 +11157,11 @@
       <c r="R69" t="n">
         <v>19.45322833368887</v>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10266,12 +11174,22 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -10386,15 +11304,17 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="P70" t="n">
-        <v>0</v>
-      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10407,12 +11327,22 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -10527,15 +11457,17 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10548,12 +11480,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -10668,15 +11610,17 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10689,12 +11633,22 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -10809,15 +11763,17 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="P73" t="n">
-        <v>0</v>
-      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10830,12 +11786,22 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -10950,15 +11916,17 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="P74" t="n">
-        <v>0</v>
-      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10971,12 +11939,22 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11097,6 +12075,11 @@
       <c r="R75" t="n">
         <v>12.75459443479473</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11109,12 +12092,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -11229,15 +12222,17 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11250,12 +12245,22 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -11370,15 +12375,17 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="P77" t="n">
-        <v>1</v>
-      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11391,12 +12398,22 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -11511,15 +12528,17 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="P78" t="n">
-        <v>0</v>
-      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11532,12 +12551,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -11652,15 +12681,17 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="P79" t="n">
-        <v>1</v>
-      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11673,12 +12704,22 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -11799,6 +12840,11 @@
       <c r="R80" t="n">
         <v>12.75459443479473</v>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11811,12 +12857,22 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -11931,15 +12987,17 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="P81" t="n">
-        <v>1</v>
-      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11952,12 +13010,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -12072,15 +13140,17 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="P82" t="n">
-        <v>1</v>
-      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12093,12 +13163,22 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -12213,15 +13293,17 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="P83" t="n">
-        <v>0</v>
-      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12234,12 +13316,22 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -12354,15 +13446,17 @@
       <c r="O84" t="n">
         <v>2</v>
       </c>
-      <c r="P84" t="n">
-        <v>2</v>
-      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0.02471820626898204</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12375,12 +13469,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -12501,6 +13605,11 @@
       <c r="R85" t="n">
         <v>7.2918708493497</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12513,12 +13622,22 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -12633,15 +13752,17 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="P86" t="n">
-        <v>1</v>
-      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0.01235910313449102</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12654,12 +13775,22 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -12774,15 +13905,17 @@
       <c r="O87" t="n">
         <v>3</v>
       </c>
-      <c r="P87" t="n">
-        <v>3</v>
-      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0.03707730940347306</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12795,12 +13928,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -12915,15 +14058,17 @@
       <c r="O88" t="n">
         <v>5</v>
       </c>
-      <c r="P88" t="n">
-        <v>5</v>
-      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0.06179551567245509</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12936,12 +14081,22 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -13056,15 +14211,17 @@
       <c r="O89" t="n">
         <v>11</v>
       </c>
-      <c r="P89" t="n">
-        <v>11</v>
-      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0.1359501344794012</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13077,12 +14234,22 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -13197,15 +14364,17 @@
       <c r="O90" t="n">
         <v>33</v>
       </c>
-      <c r="P90" t="n">
-        <v>33</v>
-      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0.4078504034382037</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13218,12 +14387,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -13344,6 +14523,11 @@
       <c r="R91" t="n">
         <v>0</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U91" t="inlineStr">
         <is>
           <t>HOLD_CH_f694197332056b74264617223b9b</t>
@@ -13361,7 +14545,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
@@ -13371,6 +14560,11 @@
       </c>
       <c r="AT91" t="n">
         <v>1</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -13491,6 +14685,11 @@
       <c r="R92" t="n">
         <v>0.2808222059060451</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>annual</t>
@@ -13503,12 +14702,22 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -13629,6 +14838,11 @@
       <c r="R93" t="n">
         <v>1.550626963046423</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>annual</t>
@@ -13641,12 +14855,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -13767,6 +14991,11 @@
       <c r="R94" t="n">
         <v>5.799589035016148</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>annual</t>
@@ -13779,12 +15008,22 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -13905,6 +15144,11 @@
       <c r="R95" t="n">
         <v>0.2930318670323949</v>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U95" t="inlineStr">
         <is>
           <t>SER_CH_TYPHOID_PARATYPHOID_COMBINED_ANNUAL</t>
@@ -13922,7 +15166,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
@@ -13932,6 +15181,11 @@
       </c>
       <c r="AT95" t="n">
         <v>1</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -14052,6 +15306,11 @@
       <c r="R96" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U96" t="inlineStr">
         <is>
           <t>HOLD_CH_f9a83f885db35bef07faa5660c7d</t>
@@ -14069,7 +15328,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
@@ -14079,6 +15343,11 @@
       </c>
       <c r="AT96" t="n">
         <v>1</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -14199,6 +15468,11 @@
       <c r="R97" t="n">
         <v>0.03662898337904936</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U97" t="inlineStr">
         <is>
           <t>HOLD_CH_469575ffcfe721f18095d3988572</t>
@@ -14216,7 +15490,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
@@ -14226,6 +15505,11 @@
       </c>
       <c r="AT97" t="n">
         <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -14346,6 +15630,11 @@
       <c r="R98" t="n">
         <v>3.687317660157635</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>annual</t>
@@ -14358,12 +15647,22 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -14484,6 +15783,11 @@
       <c r="R99" t="n">
         <v>0.04883864450539914</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U99" t="inlineStr">
         <is>
           <t>HOLD_CH_e028ac530b212500cdacefab82f4</t>
@@ -14501,7 +15805,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
@@ -14511,6 +15820,11 @@
       </c>
       <c r="AT99" t="n">
         <v>1</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -14631,6 +15945,11 @@
       <c r="R100" t="n">
         <v>0</v>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U100" t="inlineStr">
         <is>
           <t>HOLD_CH_d1b564fb561c1baf80f34e9e37f9</t>
@@ -14648,7 +15967,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
@@ -14658,6 +15982,11 @@
       </c>
       <c r="AT100" t="n">
         <v>1</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -14778,6 +16107,11 @@
       <c r="R101" t="n">
         <v>1.001192212360682</v>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>annual</t>
@@ -14790,12 +16124,22 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -14916,6 +16260,11 @@
       <c r="R102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U102" t="inlineStr">
         <is>
           <t>HOLD_CH_f886ae423245c4d4d945d22c04fa</t>
@@ -14933,7 +16282,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
@@ -14943,6 +16297,11 @@
       </c>
       <c r="AT102" t="n">
         <v>1</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -15063,6 +16422,11 @@
       <c r="R103" t="n">
         <v>0</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U103" t="inlineStr">
         <is>
           <t>HOLD_CH_b72471754ba1860d0eddb1a769dc</t>
@@ -15080,7 +16444,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
@@ -15090,6 +16459,11 @@
       </c>
       <c r="AT103" t="n">
         <v>1</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -15210,6 +16584,11 @@
       <c r="R104" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U104" t="inlineStr">
         <is>
           <t>HOLD_CH_a0517232b84d84ff4cd02f6351b8</t>
@@ -15227,7 +16606,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
@@ -15237,6 +16621,11 @@
       </c>
       <c r="AT104" t="n">
         <v>1</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -15357,6 +16746,11 @@
       <c r="R105" t="n">
         <v>1.208756451508629</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>annual</t>
@@ -15369,12 +16763,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -15495,6 +16899,11 @@
       <c r="R106" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U106" t="inlineStr">
         <is>
           <t>HOLD_CH_786c4b7daf62e750a64acefa1b6f</t>
@@ -15512,7 +16921,12 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
@@ -15522,6 +16936,11 @@
       </c>
       <c r="AT106" t="n">
         <v>1</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
@@ -15642,6 +17061,11 @@
       <c r="R107" t="n">
         <v>9.60900330643728</v>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>annual</t>
@@ -15654,12 +17078,22 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
@@ -15780,6 +17214,11 @@
       <c r="R108" t="n">
         <v>3.601850032273187</v>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>annual</t>
@@ -15792,12 +17231,22 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
@@ -15918,6 +17367,11 @@
       <c r="R109" t="n">
         <v>1.220966112634979</v>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>annual</t>
@@ -15930,12 +17384,22 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
@@ -16056,6 +17520,11 @@
       <c r="R110" t="n">
         <v>3.504172743262389</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16068,12 +17537,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -16194,6 +17673,11 @@
       <c r="R111" t="n">
         <v>0.4639671228012918</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>HOLD_CH_2ce78184086538bc0b855523c066</t>
@@ -16211,7 +17695,12 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
@@ -16221,6 +17710,11 @@
       </c>
       <c r="AT111" t="n">
         <v>1</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
@@ -16341,6 +17835,11 @@
       <c r="R112" t="n">
         <v>0.4883864450539914</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>annual</t>
@@ -16353,12 +17852,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -16479,6 +17988,11 @@
       <c r="R113" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>HOLD_CH_1e52604ac357d550ec3a557eaaa3</t>
@@ -16496,7 +18010,12 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ113" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
@@ -16506,6 +18025,11 @@
       </c>
       <c r="AT113" t="n">
         <v>1</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -16626,6 +18150,11 @@
       <c r="R114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>HOLD_CH_d2c9bee662276d35e5e8c9d18cc3</t>
@@ -16643,7 +18172,12 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ114" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
@@ -16653,6 +18187,11 @@
       </c>
       <c r="AT114" t="n">
         <v>1</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -16773,6 +18312,11 @@
       <c r="R115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>HOLD_CH_7e04405263e8990535f6c1a7374d</t>
@@ -16790,7 +18334,12 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ115" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
@@ -16800,6 +18349,11 @@
       </c>
       <c r="AT115" t="n">
         <v>1</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -16920,6 +18474,11 @@
       <c r="R116" t="n">
         <v>0.2319835614006459</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>HOLD_CH_d0b9b916925a9e694f207bd1375a</t>
@@ -16937,7 +18496,12 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
@@ -16947,6 +18511,11 @@
       </c>
       <c r="AT116" t="n">
         <v>1</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -17061,15 +18630,17 @@
       <c r="O117" t="n">
         <v>68</v>
       </c>
-      <c r="P117" t="n">
-        <v>68</v>
-      </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
         <v>0.8302569565917854</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17082,12 +18653,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -17202,15 +18783,17 @@
       <c r="O118" t="n">
         <v>69</v>
       </c>
-      <c r="P118" t="n">
-        <v>69</v>
-      </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0.8424666177181351</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17223,12 +18806,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -17343,15 +18936,17 @@
       <c r="O119" t="n">
         <v>56</v>
       </c>
-      <c r="P119" t="n">
-        <v>56</v>
-      </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
         <v>0.683741023075588</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17364,12 +18959,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -17484,15 +19089,17 @@
       <c r="O120" t="n">
         <v>74</v>
       </c>
-      <c r="P120" t="n">
-        <v>74</v>
-      </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.9035149233498841</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17505,12 +19112,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -17631,6 +19248,11 @@
       <c r="R121" t="n">
         <v>1.758191202194369</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17643,12 +19265,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -17763,15 +19395,17 @@
       <c r="O122" t="n">
         <v>148</v>
       </c>
-      <c r="P122" t="n">
-        <v>148</v>
-      </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
         <v>1.807029846699768</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17784,12 +19418,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
@@ -17904,15 +19548,17 @@
       <c r="O123" t="n">
         <v>159</v>
       </c>
-      <c r="P123" t="n">
-        <v>159</v>
-      </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
         <v>1.941336119089616</v>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -17925,12 +19571,22 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
@@ -18045,15 +19701,17 @@
       <c r="O124" t="n">
         <v>164</v>
       </c>
-      <c r="P124" t="n">
-        <v>164</v>
-      </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
         <v>2.002384424721364</v>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18066,12 +19724,22 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
@@ -18186,15 +19854,17 @@
       <c r="O125" t="n">
         <v>146</v>
       </c>
-      <c r="P125" t="n">
-        <v>146</v>
-      </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>1.782610524447068</v>
       </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18207,12 +19877,22 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
@@ -18333,6 +20013,11 @@
       <c r="R126" t="n">
         <v>0.5738540729384399</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18345,12 +20030,22 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
@@ -18465,15 +20160,17 @@
       <c r="O127" t="n">
         <v>131</v>
       </c>
-      <c r="P127" t="n">
-        <v>131</v>
-      </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>1.599465607551822</v>
       </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18486,12 +20183,22 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
@@ -18606,15 +20313,17 @@
       <c r="O128" t="n">
         <v>157</v>
       </c>
-      <c r="P128" t="n">
-        <v>157</v>
-      </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>1.916916796836916</v>
       </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18627,12 +20336,22 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
@@ -18747,15 +20466,17 @@
       <c r="O129" t="n">
         <v>109</v>
       </c>
-      <c r="P129" t="n">
-        <v>109</v>
-      </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>1.330853062772127</v>
       </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18768,12 +20489,22 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
@@ -18888,15 +20619,17 @@
       <c r="O130" t="n">
         <v>89</v>
       </c>
-      <c r="P130" t="n">
-        <v>89</v>
-      </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>1.086659840245131</v>
       </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -18909,12 +20642,22 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
@@ -19029,15 +20772,17 @@
       <c r="O131" t="n">
         <v>38</v>
       </c>
-      <c r="P131" t="n">
-        <v>38</v>
-      </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
         <v>0.4639671228012918</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19050,12 +20795,22 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
@@ -19176,6 +20931,11 @@
       <c r="R132" t="n">
         <v>4.090236477327179</v>
       </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19188,12 +20948,22 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
@@ -19308,15 +21078,17 @@
       <c r="O133" t="n">
         <v>33</v>
       </c>
-      <c r="P133" t="n">
-        <v>33</v>
-      </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
         <v>0.4029188171695429</v>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19329,12 +21101,22 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
@@ -19449,15 +21231,17 @@
       <c r="O134" t="n">
         <v>24</v>
       </c>
-      <c r="P134" t="n">
-        <v>24</v>
-      </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
         <v>0.2930318670323949</v>
       </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19470,12 +21254,22 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
@@ -19590,15 +21384,17 @@
       <c r="O135" t="n">
         <v>15</v>
       </c>
-      <c r="P135" t="n">
-        <v>15</v>
-      </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0.1831449168952468</v>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19611,12 +21407,22 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
@@ -19731,15 +21537,17 @@
       <c r="O136" t="n">
         <v>11</v>
       </c>
-      <c r="P136" t="n">
-        <v>11</v>
-      </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
         <v>0.1343062723898477</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -19752,12 +21560,22 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
@@ -19878,6 +21696,11 @@
       <c r="R137" t="n">
         <v>9.938664156848725</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19890,12 +21713,22 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
@@ -20010,15 +21843,17 @@
       <c r="O138" t="n">
         <v>7</v>
       </c>
-      <c r="P138" t="n">
-        <v>7</v>
-      </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
         <v>0.0854676278844485</v>
       </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20031,12 +21866,22 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
@@ -20151,15 +21996,17 @@
       <c r="O139" t="n">
         <v>5</v>
       </c>
-      <c r="P139" t="n">
-        <v>5</v>
-      </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
         <v>0.06104830563174893</v>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20172,12 +22019,22 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
@@ -20292,15 +22149,17 @@
       <c r="O140" t="n">
         <v>2</v>
       </c>
-      <c r="P140" t="n">
-        <v>2</v>
-      </c>
       <c r="Q140" t="n">
         <v>0</v>
       </c>
       <c r="R140" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20313,12 +22172,22 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
@@ -20433,15 +22302,17 @@
       <c r="O141" t="n">
         <v>2</v>
       </c>
-      <c r="P141" t="n">
-        <v>2</v>
-      </c>
       <c r="Q141" t="n">
         <v>0</v>
       </c>
       <c r="R141" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20454,12 +22325,22 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
@@ -20580,6 +22461,11 @@
       <c r="R142" t="n">
         <v>13.45504656123746</v>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20592,12 +22478,22 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
@@ -20712,15 +22608,17 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
       <c r="Q143" t="n">
         <v>0</v>
       </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20733,12 +22631,22 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
@@ -20853,15 +22761,17 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="P144" t="n">
-        <v>0</v>
-      </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -20874,12 +22784,22 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
@@ -20994,15 +22914,17 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="P145" t="n">
-        <v>1</v>
-      </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21015,12 +22937,22 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
@@ -21135,15 +23067,17 @@
       <c r="O146" t="n">
         <v>2</v>
       </c>
-      <c r="P146" t="n">
-        <v>2</v>
-      </c>
       <c r="Q146" t="n">
         <v>0</v>
       </c>
       <c r="R146" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21156,12 +23090,22 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
@@ -21276,15 +23220,17 @@
       <c r="O147" t="n">
         <v>3</v>
       </c>
-      <c r="P147" t="n">
-        <v>3</v>
-      </c>
       <c r="Q147" t="n">
         <v>0</v>
       </c>
       <c r="R147" t="n">
         <v>0.03662898337904936</v>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21297,12 +23243,22 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
@@ -21423,6 +23379,11 @@
       <c r="R148" t="n">
         <v>21.64772917701817</v>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21435,12 +23396,22 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
@@ -21555,15 +23526,17 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
-      <c r="P149" t="n">
-        <v>2</v>
-      </c>
       <c r="Q149" t="n">
         <v>0</v>
       </c>
       <c r="R149" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21576,12 +23549,22 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
@@ -21696,15 +23679,17 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="P150" t="n">
-        <v>1</v>
-      </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21717,12 +23702,22 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
@@ -21837,15 +23832,17 @@
       <c r="O151" t="n">
         <v>5</v>
       </c>
-      <c r="P151" t="n">
-        <v>5</v>
-      </c>
       <c r="Q151" t="n">
         <v>0</v>
       </c>
       <c r="R151" t="n">
         <v>0.06104830563174893</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21858,12 +23855,22 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
@@ -21978,15 +23985,17 @@
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="P152" t="n">
-        <v>2</v>
-      </c>
       <c r="Q152" t="n">
         <v>0</v>
       </c>
       <c r="R152" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -21999,12 +24008,22 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
@@ -22125,6 +24144,11 @@
       <c r="R153" t="n">
         <v>8.778746349845495</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22137,12 +24161,22 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
@@ -22257,15 +24291,17 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
       <c r="Q154" t="n">
         <v>0</v>
       </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22278,12 +24314,22 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
@@ -22398,15 +24444,17 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="P155" t="n">
-        <v>0</v>
-      </c>
       <c r="Q155" t="n">
         <v>0</v>
       </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22419,12 +24467,22 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
@@ -22539,15 +24597,17 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="P156" t="n">
-        <v>0</v>
-      </c>
       <c r="Q156" t="n">
         <v>0</v>
       </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22560,12 +24620,22 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
@@ -22680,15 +24750,17 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
       <c r="Q157" t="n">
         <v>0</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22701,12 +24773,22 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
@@ -22821,15 +24903,17 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
-      <c r="P158" t="n">
-        <v>1</v>
-      </c>
       <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -22842,12 +24926,22 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
@@ -22968,6 +25062,11 @@
       <c r="R159" t="n">
         <v>11.6968553590431</v>
       </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22980,12 +25079,22 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
@@ -23100,15 +25209,17 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
-      <c r="P160" t="n">
-        <v>1</v>
-      </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23121,12 +25232,22 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
@@ -23241,15 +25362,17 @@
       <c r="O161" t="n">
         <v>2</v>
       </c>
-      <c r="P161" t="n">
-        <v>2</v>
-      </c>
       <c r="Q161" t="n">
         <v>0</v>
       </c>
       <c r="R161" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23262,12 +25385,22 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
@@ -23382,15 +25515,17 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="P162" t="n">
-        <v>1</v>
-      </c>
       <c r="Q162" t="n">
         <v>0</v>
       </c>
       <c r="R162" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23403,12 +25538,22 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
@@ -23523,15 +25668,17 @@
       <c r="O163" t="n">
         <v>2</v>
       </c>
-      <c r="P163" t="n">
-        <v>2</v>
-      </c>
       <c r="Q163" t="n">
         <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23544,12 +25691,22 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
@@ -23670,6 +25827,11 @@
       <c r="R164" t="n">
         <v>8.192682615780706</v>
       </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23682,12 +25844,22 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
@@ -23802,15 +25974,17 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="P165" t="n">
-        <v>0</v>
-      </c>
       <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23823,12 +25997,22 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
@@ -23943,15 +26127,17 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="P166" t="n">
-        <v>0</v>
-      </c>
       <c r="Q166" t="n">
         <v>0</v>
       </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -23964,12 +26150,22 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
@@ -24084,15 +26280,17 @@
       <c r="O167" t="n">
         <v>4</v>
       </c>
-      <c r="P167" t="n">
-        <v>4</v>
-      </c>
       <c r="Q167" t="n">
         <v>0</v>
       </c>
       <c r="R167" t="n">
         <v>0.04883864450539914</v>
       </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24105,12 +26303,22 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
@@ -24225,15 +26433,17 @@
       <c r="O168" t="n">
         <v>0</v>
       </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
       <c r="Q168" t="n">
         <v>0</v>
       </c>
       <c r="R168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24246,12 +26456,22 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV168" t="inlineStr">
         <is>
@@ -24372,6 +26592,11 @@
       <c r="R169" t="n">
         <v>2.918109009197599</v>
       </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24384,12 +26609,22 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
+      </c>
+      <c r="AU169" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
@@ -24504,15 +26739,17 @@
       <c r="O170" t="n">
         <v>2</v>
       </c>
-      <c r="P170" t="n">
-        <v>2</v>
-      </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
         <v>0.02441932225269957</v>
       </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24525,12 +26762,22 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
@@ -24645,15 +26892,17 @@
       <c r="O171" t="n">
         <v>4</v>
       </c>
-      <c r="P171" t="n">
-        <v>4</v>
-      </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
         <v>0.04883864450539914</v>
       </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24666,12 +26915,22 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
@@ -24786,15 +27045,17 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
-      <c r="P172" t="n">
-        <v>1</v>
-      </c>
       <c r="Q172" t="n">
         <v>0</v>
       </c>
       <c r="R172" t="n">
         <v>0.01220966112634978</v>
       </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24807,12 +27068,22 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
@@ -24927,15 +27198,17 @@
       <c r="O173" t="n">
         <v>4</v>
       </c>
-      <c r="P173" t="n">
-        <v>4</v>
-      </c>
       <c r="Q173" t="n">
         <v>0</v>
       </c>
       <c r="R173" t="n">
         <v>0.04883864450539914</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -24948,12 +27221,22 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
@@ -25068,15 +27351,17 @@
       <c r="O174" t="n">
         <v>6</v>
       </c>
-      <c r="P174" t="n">
-        <v>6</v>
-      </c>
       <c r="Q174" t="n">
         <v>0</v>
       </c>
       <c r="R174" t="n">
         <v>0.07325796675809872</v>
       </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25089,12 +27374,22 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
@@ -25215,6 +27510,11 @@
       <c r="R175" t="n">
         <v>1.15991780700323</v>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25227,12 +27527,22 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
@@ -25347,15 +27657,17 @@
       <c r="O176" t="n">
         <v>12</v>
       </c>
-      <c r="P176" t="n">
-        <v>12</v>
-      </c>
       <c r="Q176" t="n">
         <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0.1465159335161974</v>
       </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25368,12 +27680,22 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR176" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
+      </c>
+      <c r="AU176" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
@@ -25488,15 +27810,17 @@
       <c r="O177" t="n">
         <v>24</v>
       </c>
-      <c r="P177" t="n">
-        <v>24</v>
-      </c>
       <c r="Q177" t="n">
         <v>0</v>
       </c>
       <c r="R177" t="n">
         <v>0.2930318670323949</v>
       </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25509,12 +27833,22 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
@@ -25629,15 +27963,17 @@
       <c r="O178" t="n">
         <v>26</v>
       </c>
-      <c r="P178" t="n">
-        <v>26</v>
-      </c>
       <c r="Q178" t="n">
         <v>0</v>
       </c>
       <c r="R178" t="n">
         <v>0.3174511892850944</v>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25650,12 +27986,22 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
@@ -25770,15 +28116,17 @@
       <c r="O179" t="n">
         <v>75</v>
       </c>
-      <c r="P179" t="n">
-        <v>75</v>
-      </c>
       <c r="Q179" t="n">
         <v>0</v>
       </c>
       <c r="R179" t="n">
         <v>0.9157245844762339</v>
       </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -25791,12 +28139,22 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
